--- a/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/stabilization/environment_input.xlsx
+++ b/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/stabilization/environment_input.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENVIRONMENT" sheetId="2" r:id="R90b547496fd64fd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENVIRONMENT" sheetId="2" r:id="R0f92aca24e794ccb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -370,7 +370,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D2" s="20" t="str">
-        <x:v>Type of medium that fill the environment (defaults to Air)</x:v>
+        <x:v>Type of medium that fills the environment (defaults to Air).</x:v>
       </x:c>
       <x:c r="E2" s="17" t="str">
         <x:v>Air</x:v>
